--- a/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,0</t>
+          <t>-4,69; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,0</t>
+          <t>-4,34; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,0</t>
+          <t>-4,69; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,0</t>
+          <t>-4,71; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,36</t>
+          <t>-3,5; -0,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,35</t>
+          <t>-3,55; -0,36</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,17</t>
+          <t>-0,86; 0,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,39</t>
+          <t>-0,72; 0,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,3</t>
+          <t>-0,4; 0,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,45</t>
+          <t>-0,34; 0,44</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,07</t>
+          <t>-0,6; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,63</t>
+          <t>-0,32; 0,77</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,45</t>
+          <t>-0,44; 0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,49</t>
+          <t>-0,44; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,0</t>
+          <t>-0,85; 0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,26</t>
+          <t>-0,72; 0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,06</t>
+          <t>-0,54; 0,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,19</t>
+          <t>-0,49; 0,16</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 201,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 172,93</t>
+          <t>-92,81; 98,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,08; 126,39</t>
+          <t>-90,12; 122,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,0</t>
+          <t>-4,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,0</t>
+          <t>-4,79; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,0</t>
+          <t>-4,78; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,0</t>
+          <t>-4,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -0,36</t>
+          <t>-3,48; -0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,36</t>
+          <t>-3,79; -0,36</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,16</t>
+          <t>-0,83; 0,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,39</t>
+          <t>-0,79; 0,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,29</t>
+          <t>-0,38; 0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,44</t>
+          <t>-0,31; 0,43</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,12</t>
+          <t>-0,79; 1,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,51</t>
+          <t>-0,32; 0,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,77</t>
+          <t>-0,32; 0,71</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,4</t>
+          <t>-0,42; 0,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,42</t>
+          <t>-0,43; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,01</t>
+          <t>-0,92; 0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,26</t>
+          <t>-0,77; 0,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,07</t>
+          <t>-0,56; 0,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,16</t>
+          <t>-0,45; 0,17</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 201,71</t>
+          <t>-100,0; 195,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,81; 98,06</t>
+          <t>-92,65; 56,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,12; 122,18</t>
+          <t>-87,15; 132,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-1,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,0</t>
+          <t>-5,32; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,0</t>
+          <t>-4,77; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,0</t>
+          <t>-4,12; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,0</t>
+          <t>-4,73; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,35</t>
+          <t>-3,43; -0,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,36</t>
+          <t>-3,32; -0,35</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>-0,86; 0,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>-0,75; 0,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,2</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,39</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,3</t>
+          <t>-0,36; 0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,43</t>
+          <t>-0,29; 0,45</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-65,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-36,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-65,42%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-36,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,61; 1,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>-1,82; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,52</t>
+          <t>-0,32; 0,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,71</t>
+          <t>-0,32; 0,63</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>14,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>-0,91; 0,0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-0,74; 0,26</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>-0,42; 0,45</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,43; 0,41</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 0,01</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,24</t>
+          <t>-0,44; 0,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,05</t>
+          <t>-0,54; 0,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,17</t>
+          <t>-0,46; 0,19</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-79,69%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-42,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-18,88%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-35,28%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-79,69%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-42,06%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,65; 56,74</t>
+          <t>-100,0; 172,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,15; 132,19</t>
+          <t>-88,08; 126,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,275 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.545858946414424</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.545858946414424</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.336550272313683</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.336550272313683</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.438835665157723</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.438835665157723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,73; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; -0,36</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-3,32; -0,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.316841549268931</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.765906597215934</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.12015231768776</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.732468710594966</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.433117133255998</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-3.322399066707498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.3627834559223237</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.3459304025344226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,86; 0,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 0,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,23</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 0,3</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 0,45</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-65,42%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-36,05%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.2640382450142593</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1454895647806605</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1991930861191272</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.2463435748971335</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.04753599369601191</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.03676550044431379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.8559641900013395</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.7458495140248628</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.3606268323791851</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.2944106121463191</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1664992269656959</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3867092745779392</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9994784933781297</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.231591532614994</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.2977350377079814</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.4472848525951768</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 1,07</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 0,51</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 0,63</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.6541778148180706</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3604631047366062</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2205114223525574</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1705489286355105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +876,273 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3689849424371651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04259936141379331</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3007993077296526</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.0109180942171079</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.03445833017053977</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 0,0</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 0,26</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 0,45</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,44; 0,49</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 0,06</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 0,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.6084384121407591</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.821066206539825</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.3168989406423282</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.3165128175958025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-79,69%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-42,06%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-18,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-35,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-58,55%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-39,72%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="n">
+        <v>2.162838819969044</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.06675083523307</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.5138849965104365</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.6253119810280607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 172,93</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-88,08; 126,39</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.1416205433959312</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.06927250297197093</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2186292526590937</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.3606627681774024</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1903533817813846</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.04818723565018432</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.09003955702199516</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.2089110674573744</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.1417217704507959</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.9105731103443396</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.7413934696014458</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.4192199854050008</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.437637208625497</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.5405644146765994</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.4638227446828475</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.2578541576844587</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.4475622208524304</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.4850376845255568</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.05933936580389976</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.1868910076443501</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.796853087720664</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.4205692780463458</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.1888094885339736</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.3527972185946183</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.5855239040994923</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3972096133546077</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.8808432207554617</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>1.729301010481144</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.263875535584463</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1150,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
